--- a/data/trans_dic/IP1005-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen anomalía congénita</t>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,04</t>
+          <t>0,1; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,23</t>
+          <t>0,14; 1,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,7 +823,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,66</t>
+          <t>0,07; 0,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,55</t>
+          <t>0,18; 1,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,52</t>
+          <t>0,17; 1,51</t>
         </is>
       </c>
     </row>
@@ -1007,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,73</t>
+          <t>0,06; 0,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,75</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,14</t>
+          <t>0,2; 1,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,6</t>
+          <t>0,1; 0,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,75</t>
+          <t>0,23; 0,76</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2811</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4690</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4206</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3476</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>472; 4758</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3390</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4740</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>675; 6164</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3402</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>673; 5469</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1702; 8403</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4647</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3720</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3489</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3375</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4425</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>601; 5712</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4063</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>606; 5442</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>633; 5188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>442; 5273</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>604; 5967</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>602; 5276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4732</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1469; 8101</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1379; 8855</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1123; 7119</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11035</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1005-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,22 +803,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,26</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,87</t>
+          <t>0,18; 0,82</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,72</t>
+          <t>0,18; 1,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,51</t>
+          <t>0,17; 1,53</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,76</t>
+          <t>0,09; 0,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,75</t>
+          <t>0,06; 0,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,07; 0,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,08; 0,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,09</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,63</t>
+          <t>0,1; 0,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,49</t>
+          <t>0,08; 0,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,76</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2811</t>
+          <t>0; 3488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4690</t>
+          <t>0; 4158</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1474,42 +1474,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 3960</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>472; 4758</t>
+          <t>473; 4774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3390</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4740</t>
+          <t>0; 5091</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>675; 6164</t>
+          <t>681; 6710</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3402</t>
+          <t>0; 3076</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>673; 5469</t>
+          <t>671; 5468</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1702; 8403</t>
+          <t>1775; 7912</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4647</t>
+          <t>0; 4578</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3720</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3375</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4425</t>
+          <t>0; 4395</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>601; 5712</t>
+          <t>604; 5159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4063</t>
+          <t>0; 4024</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>606; 5442</t>
+          <t>598; 5502</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>633; 5188</t>
+          <t>633; 4664</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>442; 5273</t>
+          <t>437; 4903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>604; 5967</t>
+          <t>484; 5665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>602; 5276</t>
+          <t>601; 5409</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4732</t>
+          <t>0; 5764</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1469; 8101</t>
+          <t>1383; 8190</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1379; 8855</t>
+          <t>1375; 8537</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1123; 7119</t>
+          <t>1118; 6906</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3278; 11035</t>
+          <t>3201; 11555</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1005-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,82</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 1,23</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 1,01</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,85</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,37</t>
+          <t>0,1; 1,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,58</t>
+          <t>0,07; 0,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,82</t>
+          <t>0,18; 0,87</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,34 +898,34 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,35</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,61</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,76</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,52</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,34</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>0,18; 1,55</t>
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,53</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,68</t>
+          <t>0,08; 0,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,69</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,18; 1,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,75</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,06; 0,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,1</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,61</t>
+          <t>0,1; 0,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,47</t>
+          <t>0,08; 0,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,21; 0,75</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1253,22 +1253,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>642</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 3531</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3488</t>
+          <t>0; 3901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4158</t>
+          <t>0; 4129</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1715</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 3407</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>680; 6031</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3960</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>473; 4774</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4064</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5091</t>
+          <t>0; 4027</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>681; 6710</t>
+          <t>474; 4922</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3076</t>
+          <t>0; 3382</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>671; 5468</t>
+          <t>670; 6171</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1775; 7912</t>
+          <t>1744; 8386</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1104</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>604</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1381</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4578</t>
+          <t>0; 2677</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3045</t>
+          <t>0; 4398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 4535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3801</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4395</t>
+          <t>0; 3041</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>604; 5159</t>
+          <t>600; 5135</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4024</t>
+          <t>0; 3746</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>598; 5502</t>
+          <t>605; 5476</t>
         </is>
       </c>
     </row>
@@ -1694,27 +1694,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2319</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>633; 4664</t>
+          <t>602; 5389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>437; 4903</t>
+          <t>0; 4062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>484; 5665</t>
+          <t>1359; 8470</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>601; 5409</t>
+          <t>632; 5742</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5764</t>
+          <t>442; 5184</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1383; 8190</t>
+          <t>605; 5496</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1375; 8537</t>
+          <t>1336; 8439</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1118; 6906</t>
+          <t>1114; 7101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3201; 11555</t>
+          <t>3054; 10897</t>
         </is>
       </c>
     </row>
